--- a/MS Excel Crash Course/Lecture 15.xlsx
+++ b/MS Excel Crash Course/Lecture 15.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AR Boot Camp 2k26\MS Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AR Boot Camp 2k26\MS Excel Crash Course\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D36C7004-068D-4D3A-B649-42A6423C49EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{750CA239-075F-492C-A4ED-90CE77CBABDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>Convert Text to Number</t>
   </si>
@@ -47,14 +47,17 @@
     <t>Convert Number to Text</t>
   </si>
   <si>
-    <t>Under Development</t>
+    <t>Text</t>
+  </si>
+  <si>
+    <t>Number</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -70,16 +73,36 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -87,14 +110,35 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -377,65 +421,120 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="31.5" x14ac:dyDescent="0.5">
-      <c r="A1" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="D1" t="s">
+      <c r="B1" s="4"/>
+      <c r="D1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="E1" s="4"/>
+      <c r="H1" s="1"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>45</v>
+      </c>
+      <c r="B2" s="3">
+        <f>A2*1</f>
+        <v>45</v>
+      </c>
+      <c r="D2" s="3">
+        <v>45</v>
+      </c>
+      <c r="E2" s="2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>56</v>
+      </c>
+      <c r="B3" s="3">
+        <f t="shared" ref="B3:B7" si="0">A3*1</f>
+        <v>56</v>
+      </c>
+      <c r="D3" s="3">
+        <v>56</v>
+      </c>
+      <c r="E3" s="2">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>72</v>
+      </c>
+      <c r="B4" s="3">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="D4" s="3">
+        <v>72</v>
+      </c>
+      <c r="E4" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>23</v>
+      </c>
+      <c r="B5" s="3">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="D5" s="3">
+        <v>23</v>
+      </c>
+      <c r="E5" s="2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>12</v>
+      </c>
+      <c r="B6" s="3">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="D6" s="3">
+        <v>12</v>
+      </c>
+      <c r="E6" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>45</v>
-      </c>
-      <c r="D2">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>56</v>
-      </c>
-      <c r="D3">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>72</v>
-      </c>
-      <c r="D4">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>23</v>
-      </c>
-      <c r="D5">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>12</v>
-      </c>
-      <c r="D6">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <f>SUM(A2:A6)</f>
+      <c r="B7" s="6">
+        <f>SUM(B2:B6)</f>
         <v>208</v>
       </c>
+      <c r="D7" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7" s="5">
+        <f>SUM(E2:E6)</f>
+        <v>208</v>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="D1:E1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>